--- a/bgimg/A+與A活動公版管理表.xlsx
+++ b/bgimg/A+與A活動公版管理表.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aplus" sheetId="1" r:id="R38e0446effca4fbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aplus(PSD路徑)" sheetId="2" r:id="Rdd652d7deb9e45d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A" sheetId="3" r:id="Re363d216116e4412"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a(PSD路徑)" sheetId="4" r:id="Refee341db7274de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#分類規則" sheetId="5" r:id="Rc2811e0ee2fa49e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aplus" sheetId="1" r:id="R51642d60d3de4677"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aplus(PSD路徑)" sheetId="2" r:id="R54ef11487b3841ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A" sheetId="3" r:id="Rc87c3499712f4c6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a(PSD路徑)" sheetId="4" r:id="R2cb83b56f28043da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#分類規則" sheetId="5" r:id="Rac6e61c6b49b4dce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19215,9 +19215,7 @@
       <x:c r="B11" s="5" t="s">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>黑金色系</x:v>
-      </x:c>
+      <x:c r="C11" s="5"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5"/>
